--- a/SUM.NZ/Reports/SUM.NZ_DCF_Model.xlsx
+++ b/SUM.NZ/Reports/SUM.NZ_DCF_Model.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
